--- a/originales/respuestas/2025/01. Calificadas/bucle p32/Agencia Distrital Para La Educación Superior, La Ciencia Y La Tecnología.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p32/Agencia Distrital Para La Educación Superior, La Ciencia Y La Tecnología.xlsx
@@ -69,23 +69,21 @@
     <t>Museo</t>
   </si>
   <si>
-    <t>Agencia Distrital Para La Educación Superior, La Ciencia Y La Tecnología</t>
-  </si>
-  <si>
-    <t>Laboratorios de Innovación Pública</t>
-  </si>
-  <si>
-    <t>Equipo de innovación pública - Gerencia de Estrategia</t>
-  </si>
-  <si>
-    <t>🧠 Naturaleza de la unidad: No es una oficina formalizada mediante acto administrativo, pero funciona como un equipo transversal y núcleo articulador de innovación dentro de la entidad.
- 🎯 Misión: La unidad tiene como propósito fortalecer capacidades internas, facilitar procesos de diseño de soluciones, promover una cultura de innovación y sistematizar aprendizajes.</t>
-  </si>
-  <si>
-    <t>🎯 Funciones: Sus funciones incluyen
- 1. Diseño de soluciones Acompañamiento a retos estratégicos mediante la metodología Tejido iBO, incluyendo diagnóstico, ideación, prototipado y validación. 
- 2. Fortalecimiento de capacidades Formación interna en innovación pública a través de cápsulas, talleres, entre otras.
- 3. Relacionamiento con el ecosistema Articulación con laboratorios de innovación para intercambiar buenas prácticas.</t>
+    <t>Instituto Distrital de participación y acción comunal</t>
+  </si>
+  <si>
+    <t>Laboratorios de Innovación Pública
+Mesas de Participación Ciudadana
+Laboratorios de Gobierno Abierto</t>
+  </si>
+  <si>
+    <t>Particilab</t>
+  </si>
+  <si>
+    <t>Crear espacios para promover la participación incidente por parte de la ciudadanía, la inteligencia colectiva y promover las soluciones innovadoras a las diferentes problemáticas de la ciudad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Innovación pública y social para la participación.</t>
   </si>
   <si>
     <t>Relevancia del tipo de unidad</t>
@@ -230,13 +228,13 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -527,39 +525,29 @@
         <v>21</v>
       </c>
       <c r="F2" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="G2" s="5" t="s">
+        <v>7.0</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="I2" s="5" t="s">
+      <c r="H2" s="5"/>
+      <c r="I2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="K2" s="5" t="s">
+      <c r="J2" s="5"/>
+      <c r="K2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="M2" s="5" t="s">
+      <c r="L2" s="5"/>
+      <c r="M2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="O2" s="5" t="s">
+      <c r="N2" s="5"/>
+      <c r="O2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="Q2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="6"/>
     </row>
     <row r="3" ht="14.25" customHeight="1"/>
     <row r="4" ht="14.25" customHeight="1"/>
